--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/poppy.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/poppy.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Au-au!  </t>
+          <t>Ruff-ruff!</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eu te levo.  </t>
+          <t>Vou te levar.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uau! </t>
+          <t>Au!</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Au-au! </t>
+          <t>Ruff-ruff!</t>
         </is>
       </c>
     </row>
